--- a/www_Test _new_lot_rull/prodout/print.xlsx
+++ b/www_Test _new_lot_rull/prodout/print.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId4"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
   <si>
     <t>Drum 出 貨 檢 查 表</t>
   </si>
@@ -32,22 +32,16 @@
     <t>檢查日期</t>
   </si>
   <si>
-    <t>2024-09-02</t>
-  </si>
-  <si>
     <t>出荷日期</t>
-  </si>
-  <si>
-    <t>2024-09-03</t>
   </si>
   <si>
     <t>客戶名稱</t>
   </si>
   <si>
-    <t>中國砂輪-W</t>
+    <t>出荷決定書No.</t>
   </si>
   <si>
-    <t>出荷決定書No.</t>
+    <t>SA20-2308081747</t>
   </si>
   <si>
     <t>品名</t>
@@ -65,24 +59,6 @@
     <t>數量</t>
   </si>
   <si>
-    <t>HCL鹽酸</t>
-  </si>
-  <si>
-    <t>鹽酸 20KG</t>
-  </si>
-  <si>
-    <t>C324F17</t>
-  </si>
-  <si>
-    <t>2025-03-17</t>
-  </si>
-  <si>
-    <t>C324F21</t>
-  </si>
-  <si>
-    <t>2025-03-21</t>
-  </si>
-  <si>
     <t>桶號</t>
   </si>
   <si>
@@ -90,105 +66,6 @@
   </si>
   <si>
     <t>棧板No.</t>
-  </si>
-  <si>
-    <t>CS400109</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>CS400209</t>
-  </si>
-  <si>
-    <t>CS400309</t>
-  </si>
-  <si>
-    <t>CS400409</t>
-  </si>
-  <si>
-    <t>CS400509</t>
-  </si>
-  <si>
-    <t>CS400609</t>
-  </si>
-  <si>
-    <t>CS400709</t>
-  </si>
-  <si>
-    <t>CS400809</t>
-  </si>
-  <si>
-    <t>CS400909</t>
-  </si>
-  <si>
-    <t>CS401009</t>
-  </si>
-  <si>
-    <t>CS401109</t>
-  </si>
-  <si>
-    <t>CS401209</t>
-  </si>
-  <si>
-    <t>CS401309</t>
-  </si>
-  <si>
-    <t>CS401409</t>
-  </si>
-  <si>
-    <t>CS401509</t>
-  </si>
-  <si>
-    <t>CS401609</t>
-  </si>
-  <si>
-    <t>CS401709</t>
-  </si>
-  <si>
-    <t>CS401809</t>
-  </si>
-  <si>
-    <t>CS401909</t>
-  </si>
-  <si>
-    <t>CS402009</t>
-  </si>
-  <si>
-    <t>CS402109</t>
-  </si>
-  <si>
-    <t>CS402209</t>
-  </si>
-  <si>
-    <t>CS402309</t>
-  </si>
-  <si>
-    <t>CS402409</t>
-  </si>
-  <si>
-    <t>CS402509</t>
-  </si>
-  <si>
-    <t>CS402609</t>
-  </si>
-  <si>
-    <t>CS402709</t>
-  </si>
-  <si>
-    <t>CS402809</t>
-  </si>
-  <si>
-    <t>CS402909</t>
-  </si>
-  <si>
-    <t>CS403009</t>
-  </si>
-  <si>
-    <t>CS403109</t>
-  </si>
-  <si>
-    <t>CS403209</t>
   </si>
   <si>
     <t>主管</t>
@@ -200,58 +77,7 @@
     <t>擔當</t>
   </si>
   <si>
-    <t>洪書立</t>
-  </si>
-  <si>
     <t>（QSELPC2004-001A9）</t>
-  </si>
-  <si>
-    <t>CS403309</t>
-  </si>
-  <si>
-    <t>CS403409</t>
-  </si>
-  <si>
-    <t>CS403509</t>
-  </si>
-  <si>
-    <t>CS403609</t>
-  </si>
-  <si>
-    <t>CS403709</t>
-  </si>
-  <si>
-    <t>CS403809</t>
-  </si>
-  <si>
-    <t>CS403909</t>
-  </si>
-  <si>
-    <t>CS404009</t>
-  </si>
-  <si>
-    <t>CS404109</t>
-  </si>
-  <si>
-    <t>CS404209</t>
-  </si>
-  <si>
-    <t>CS404309</t>
-  </si>
-  <si>
-    <t>CS404409</t>
-  </si>
-  <si>
-    <t>CS404509</t>
-  </si>
-  <si>
-    <t>CS404609</t>
-  </si>
-  <si>
-    <t>CS404709</t>
-  </si>
-  <si>
-    <t>CS404809</t>
   </si>
 </sst>
 </file>
@@ -1103,134 +929,108 @@
         <v>1</v>
       </c>
       <c r="B2" s="12"/>
-      <c r="C2" s="12" t="s">
-        <v>2</v>
-      </c>
+      <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="12"/>
-      <c r="G2" s="12" t="s">
-        <v>4</v>
-      </c>
+      <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2" s="12"/>
-      <c r="L2" s="12" t="s">
-        <v>6</v>
-      </c>
+      <c r="L2" s="12"/>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R2" s="12"/>
-      <c r="S2" s="46">
-        <v>202408300010560</v>
+      <c r="S2" s="46" t="s">
+        <v>5</v>
       </c>
       <c r="T2" s="47"/>
     </row>
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" s="48"/>
     </row>
     <row r="5" spans="1:22" customHeight="1" ht="18">
-      <c r="A5" s="24" t="s">
-        <v>13</v>
-      </c>
+      <c r="A5" s="24"/>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="E5" s="25"/>
-      <c r="F5" s="23" t="s">
-        <v>14</v>
-      </c>
+      <c r="F5" s="23"/>
       <c r="G5" s="23"/>
       <c r="H5" s="23"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="20" t="s">
-        <v>15</v>
-      </c>
+      <c r="J5" s="20"/>
       <c r="K5" s="21"/>
       <c r="L5" s="21"/>
       <c r="M5" s="21"/>
       <c r="N5" s="22"/>
-      <c r="O5" s="20" t="s">
-        <v>16</v>
-      </c>
+      <c r="O5" s="20"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="21"/>
       <c r="R5" s="22"/>
-      <c r="S5" s="25">
-        <v>16</v>
-      </c>
+      <c r="S5" s="25"/>
       <c r="T5" s="45"/>
     </row>
     <row r="6" spans="1:22" customHeight="1" ht="18">
-      <c r="A6" s="24" t="s">
-        <v>13</v>
-      </c>
+      <c r="A6" s="24"/>
       <c r="B6" s="25"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
-      <c r="F6" s="23" t="s">
-        <v>14</v>
-      </c>
+      <c r="F6" s="23"/>
       <c r="G6" s="23"/>
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="20" t="s">
-        <v>17</v>
-      </c>
+      <c r="J6" s="20"/>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
       <c r="M6" s="21"/>
       <c r="N6" s="22"/>
-      <c r="O6" s="20" t="s">
-        <v>18</v>
-      </c>
+      <c r="O6" s="20"/>
       <c r="P6" s="21"/>
       <c r="Q6" s="21"/>
       <c r="R6" s="22"/>
-      <c r="S6" s="25">
-        <v>32</v>
-      </c>
+      <c r="S6" s="25"/>
       <c r="T6" s="45"/>
     </row>
     <row r="7" spans="1:22" customHeight="1" ht="18">
@@ -1319,649 +1119,393 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A12" s="42" t="s">
-        <v>15</v>
-      </c>
+      <c r="A12" s="42"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
-      <c r="D12" s="23" t="s">
-        <v>22</v>
-      </c>
+      <c r="D12" s="23"/>
       <c r="E12" s="23"/>
-      <c r="F12" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F12" s="35"/>
       <c r="G12" s="35"/>
       <c r="H12" s="35"/>
-      <c r="I12" s="35">
-        <v>1</v>
-      </c>
+      <c r="I12" s="35"/>
       <c r="J12" s="35"/>
-      <c r="K12" s="23" t="s">
-        <v>15</v>
-      </c>
+      <c r="K12" s="23"/>
       <c r="L12" s="23"/>
-      <c r="M12" s="23" t="s">
-        <v>24</v>
-      </c>
+      <c r="M12" s="23"/>
       <c r="N12" s="23"/>
       <c r="O12" s="23"/>
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R12" s="35"/>
       <c r="S12" s="35"/>
-      <c r="T12" s="9">
-        <v>1</v>
-      </c>
+      <c r="T12" s="9"/>
     </row>
     <row r="13" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A13" s="24" t="s">
-        <v>15</v>
-      </c>
+      <c r="A13" s="24"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
-      <c r="D13" s="23" t="s">
-        <v>25</v>
-      </c>
+      <c r="D13" s="23"/>
       <c r="E13" s="23"/>
-      <c r="F13" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F13" s="35"/>
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
-      <c r="I13" s="35">
-        <v>1</v>
-      </c>
+      <c r="I13" s="35"/>
       <c r="J13" s="35"/>
-      <c r="K13" s="23" t="s">
-        <v>15</v>
-      </c>
+      <c r="K13" s="23"/>
       <c r="L13" s="23"/>
-      <c r="M13" s="23" t="s">
-        <v>26</v>
-      </c>
+      <c r="M13" s="23"/>
       <c r="N13" s="23"/>
       <c r="O13" s="23"/>
       <c r="P13" s="23"/>
       <c r="Q13" s="23"/>
-      <c r="R13" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R13" s="35"/>
       <c r="S13" s="35"/>
-      <c r="T13" s="9">
-        <v>1</v>
-      </c>
+      <c r="T13" s="9"/>
     </row>
     <row r="14" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A14" s="24" t="s">
-        <v>15</v>
-      </c>
+      <c r="A14" s="24"/>
       <c r="B14" s="25"/>
       <c r="C14" s="25"/>
-      <c r="D14" s="23" t="s">
-        <v>27</v>
-      </c>
+      <c r="D14" s="23"/>
       <c r="E14" s="23"/>
-      <c r="F14" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F14" s="35"/>
       <c r="G14" s="35"/>
       <c r="H14" s="35"/>
-      <c r="I14" s="35">
-        <v>1</v>
-      </c>
+      <c r="I14" s="35"/>
       <c r="J14" s="35"/>
-      <c r="K14" s="23" t="s">
-        <v>15</v>
-      </c>
+      <c r="K14" s="23"/>
       <c r="L14" s="23"/>
-      <c r="M14" s="23" t="s">
-        <v>28</v>
-      </c>
+      <c r="M14" s="23"/>
       <c r="N14" s="23"/>
       <c r="O14" s="23"/>
       <c r="P14" s="23"/>
       <c r="Q14" s="23"/>
-      <c r="R14" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R14" s="35"/>
       <c r="S14" s="35"/>
-      <c r="T14" s="9">
-        <v>1</v>
-      </c>
+      <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A15" s="24" t="s">
-        <v>15</v>
-      </c>
+      <c r="A15" s="24"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
-      <c r="D15" s="23" t="s">
-        <v>29</v>
-      </c>
+      <c r="D15" s="23"/>
       <c r="E15" s="23"/>
-      <c r="F15" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F15" s="35"/>
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
-      <c r="I15" s="35">
-        <v>1</v>
-      </c>
+      <c r="I15" s="35"/>
       <c r="J15" s="35"/>
-      <c r="K15" s="23" t="s">
-        <v>15</v>
-      </c>
+      <c r="K15" s="23"/>
       <c r="L15" s="23"/>
-      <c r="M15" s="23" t="s">
-        <v>30</v>
-      </c>
+      <c r="M15" s="23"/>
       <c r="N15" s="23"/>
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R15" s="35"/>
       <c r="S15" s="35"/>
-      <c r="T15" s="9">
-        <v>1</v>
-      </c>
+      <c r="T15" s="9"/>
     </row>
     <row r="16" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A16" s="24" t="s">
-        <v>15</v>
-      </c>
+      <c r="A16" s="24"/>
       <c r="B16" s="25"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="23" t="s">
-        <v>31</v>
-      </c>
+      <c r="D16" s="23"/>
       <c r="E16" s="23"/>
-      <c r="F16" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F16" s="35"/>
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
-      <c r="I16" s="35">
-        <v>1</v>
-      </c>
+      <c r="I16" s="35"/>
       <c r="J16" s="35"/>
-      <c r="K16" s="23" t="s">
-        <v>15</v>
-      </c>
+      <c r="K16" s="23"/>
       <c r="L16" s="23"/>
-      <c r="M16" s="23" t="s">
-        <v>32</v>
-      </c>
+      <c r="M16" s="23"/>
       <c r="N16" s="23"/>
       <c r="O16" s="23"/>
       <c r="P16" s="23"/>
       <c r="Q16" s="23"/>
-      <c r="R16" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R16" s="35"/>
       <c r="S16" s="35"/>
-      <c r="T16" s="9">
-        <v>1</v>
-      </c>
+      <c r="T16" s="9"/>
     </row>
     <row r="17" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A17" s="24" t="s">
-        <v>15</v>
-      </c>
+      <c r="A17" s="24"/>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
-      <c r="D17" s="23" t="s">
-        <v>33</v>
-      </c>
+      <c r="D17" s="23"/>
       <c r="E17" s="23"/>
-      <c r="F17" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F17" s="35"/>
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
-      <c r="I17" s="35">
-        <v>1</v>
-      </c>
+      <c r="I17" s="35"/>
       <c r="J17" s="35"/>
-      <c r="K17" s="23" t="s">
-        <v>15</v>
-      </c>
+      <c r="K17" s="23"/>
       <c r="L17" s="23"/>
-      <c r="M17" s="23" t="s">
-        <v>34</v>
-      </c>
+      <c r="M17" s="23"/>
       <c r="N17" s="23"/>
       <c r="O17" s="23"/>
       <c r="P17" s="23"/>
       <c r="Q17" s="23"/>
-      <c r="R17" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R17" s="35"/>
       <c r="S17" s="35"/>
-      <c r="T17" s="9">
-        <v>1</v>
-      </c>
+      <c r="T17" s="9"/>
     </row>
     <row r="18" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A18" s="24" t="s">
-        <v>15</v>
-      </c>
+      <c r="A18" s="24"/>
       <c r="B18" s="25"/>
       <c r="C18" s="25"/>
-      <c r="D18" s="23" t="s">
-        <v>35</v>
-      </c>
+      <c r="D18" s="23"/>
       <c r="E18" s="23"/>
-      <c r="F18" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F18" s="35"/>
       <c r="G18" s="35"/>
       <c r="H18" s="35"/>
-      <c r="I18" s="35">
-        <v>1</v>
-      </c>
+      <c r="I18" s="35"/>
       <c r="J18" s="35"/>
-      <c r="K18" s="23" t="s">
-        <v>15</v>
-      </c>
+      <c r="K18" s="23"/>
       <c r="L18" s="23"/>
-      <c r="M18" s="23" t="s">
-        <v>36</v>
-      </c>
+      <c r="M18" s="23"/>
       <c r="N18" s="23"/>
       <c r="O18" s="23"/>
       <c r="P18" s="23"/>
       <c r="Q18" s="23"/>
-      <c r="R18" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R18" s="35"/>
       <c r="S18" s="35"/>
-      <c r="T18" s="9">
-        <v>1</v>
-      </c>
+      <c r="T18" s="9"/>
     </row>
     <row r="19" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A19" s="24" t="s">
-        <v>15</v>
-      </c>
+      <c r="A19" s="24"/>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
-      <c r="D19" s="23" t="s">
-        <v>37</v>
-      </c>
+      <c r="D19" s="23"/>
       <c r="E19" s="23"/>
-      <c r="F19" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F19" s="35"/>
       <c r="G19" s="35"/>
       <c r="H19" s="35"/>
-      <c r="I19" s="35">
-        <v>1</v>
-      </c>
+      <c r="I19" s="35"/>
       <c r="J19" s="35"/>
-      <c r="K19" s="23" t="s">
-        <v>15</v>
-      </c>
+      <c r="K19" s="23"/>
       <c r="L19" s="23"/>
-      <c r="M19" s="23" t="s">
-        <v>38</v>
-      </c>
+      <c r="M19" s="23"/>
       <c r="N19" s="23"/>
       <c r="O19" s="23"/>
       <c r="P19" s="23"/>
       <c r="Q19" s="23"/>
-      <c r="R19" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R19" s="35"/>
       <c r="S19" s="35"/>
-      <c r="T19" s="9">
-        <v>1</v>
-      </c>
+      <c r="T19" s="9"/>
     </row>
     <row r="20" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A20" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="A20" s="24"/>
       <c r="B20" s="25"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="23" t="s">
-        <v>39</v>
-      </c>
+      <c r="D20" s="23"/>
       <c r="E20" s="23"/>
-      <c r="F20" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F20" s="35"/>
       <c r="G20" s="35"/>
       <c r="H20" s="35"/>
-      <c r="I20" s="35">
-        <v>1</v>
-      </c>
+      <c r="I20" s="35"/>
       <c r="J20" s="35"/>
-      <c r="K20" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K20" s="23"/>
       <c r="L20" s="23"/>
-      <c r="M20" s="23" t="s">
-        <v>40</v>
-      </c>
+      <c r="M20" s="23"/>
       <c r="N20" s="23"/>
       <c r="O20" s="23"/>
       <c r="P20" s="23"/>
       <c r="Q20" s="23"/>
-      <c r="R20" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R20" s="35"/>
       <c r="S20" s="35"/>
-      <c r="T20" s="9">
-        <v>1</v>
-      </c>
+      <c r="T20" s="9"/>
     </row>
     <row r="21" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A21" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="A21" s="24"/>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
-      <c r="D21" s="23" t="s">
-        <v>41</v>
-      </c>
+      <c r="D21" s="23"/>
       <c r="E21" s="23"/>
-      <c r="F21" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F21" s="35"/>
       <c r="G21" s="35"/>
       <c r="H21" s="35"/>
-      <c r="I21" s="35">
-        <v>1</v>
-      </c>
+      <c r="I21" s="35"/>
       <c r="J21" s="35"/>
-      <c r="K21" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K21" s="23"/>
       <c r="L21" s="23"/>
-      <c r="M21" s="23" t="s">
-        <v>42</v>
-      </c>
+      <c r="M21" s="23"/>
       <c r="N21" s="23"/>
       <c r="O21" s="23"/>
       <c r="P21" s="23"/>
       <c r="Q21" s="23"/>
-      <c r="R21" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R21" s="35"/>
       <c r="S21" s="35"/>
-      <c r="T21" s="9">
-        <v>1</v>
-      </c>
+      <c r="T21" s="9"/>
     </row>
     <row r="22" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A22" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="A22" s="24"/>
       <c r="B22" s="25"/>
       <c r="C22" s="25"/>
-      <c r="D22" s="23" t="s">
-        <v>43</v>
-      </c>
+      <c r="D22" s="23"/>
       <c r="E22" s="23"/>
-      <c r="F22" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F22" s="35"/>
       <c r="G22" s="35"/>
       <c r="H22" s="35"/>
-      <c r="I22" s="35">
-        <v>1</v>
-      </c>
+      <c r="I22" s="35"/>
       <c r="J22" s="35"/>
-      <c r="K22" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K22" s="23"/>
       <c r="L22" s="23"/>
-      <c r="M22" s="23" t="s">
-        <v>44</v>
-      </c>
+      <c r="M22" s="23"/>
       <c r="N22" s="23"/>
       <c r="O22" s="23"/>
       <c r="P22" s="23"/>
       <c r="Q22" s="23"/>
-      <c r="R22" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R22" s="35"/>
       <c r="S22" s="35"/>
-      <c r="T22" s="9">
-        <v>1</v>
-      </c>
+      <c r="T22" s="9"/>
     </row>
     <row r="23" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A23" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="A23" s="24"/>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
-      <c r="D23" s="23" t="s">
-        <v>45</v>
-      </c>
+      <c r="D23" s="23"/>
       <c r="E23" s="23"/>
-      <c r="F23" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F23" s="35"/>
       <c r="G23" s="35"/>
       <c r="H23" s="35"/>
-      <c r="I23" s="35">
-        <v>1</v>
-      </c>
+      <c r="I23" s="35"/>
       <c r="J23" s="35"/>
-      <c r="K23" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K23" s="23"/>
       <c r="L23" s="23"/>
-      <c r="M23" s="23" t="s">
-        <v>46</v>
-      </c>
+      <c r="M23" s="23"/>
       <c r="N23" s="23"/>
       <c r="O23" s="23"/>
       <c r="P23" s="23"/>
       <c r="Q23" s="23"/>
-      <c r="R23" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R23" s="35"/>
       <c r="S23" s="35"/>
-      <c r="T23" s="9">
-        <v>1</v>
-      </c>
+      <c r="T23" s="9"/>
     </row>
     <row r="24" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A24" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="A24" s="24"/>
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
-      <c r="D24" s="23" t="s">
-        <v>47</v>
-      </c>
+      <c r="D24" s="23"/>
       <c r="E24" s="23"/>
-      <c r="F24" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F24" s="35"/>
       <c r="G24" s="35"/>
       <c r="H24" s="35"/>
-      <c r="I24" s="35">
-        <v>1</v>
-      </c>
+      <c r="I24" s="35"/>
       <c r="J24" s="35"/>
-      <c r="K24" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K24" s="23"/>
       <c r="L24" s="23"/>
-      <c r="M24" s="23" t="s">
-        <v>48</v>
-      </c>
+      <c r="M24" s="23"/>
       <c r="N24" s="23"/>
       <c r="O24" s="23"/>
       <c r="P24" s="23"/>
       <c r="Q24" s="23"/>
-      <c r="R24" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R24" s="35"/>
       <c r="S24" s="35"/>
-      <c r="T24" s="9">
-        <v>1</v>
-      </c>
+      <c r="T24" s="9"/>
     </row>
     <row r="25" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A25" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="A25" s="24"/>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
-      <c r="D25" s="23" t="s">
-        <v>49</v>
-      </c>
+      <c r="D25" s="23"/>
       <c r="E25" s="23"/>
-      <c r="F25" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F25" s="35"/>
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
-      <c r="I25" s="35">
-        <v>1</v>
-      </c>
+      <c r="I25" s="35"/>
       <c r="J25" s="35"/>
-      <c r="K25" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K25" s="23"/>
       <c r="L25" s="23"/>
-      <c r="M25" s="23" t="s">
-        <v>50</v>
-      </c>
+      <c r="M25" s="23"/>
       <c r="N25" s="23"/>
       <c r="O25" s="23"/>
       <c r="P25" s="23"/>
       <c r="Q25" s="23"/>
-      <c r="R25" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R25" s="35"/>
       <c r="S25" s="35"/>
-      <c r="T25" s="9">
-        <v>1</v>
-      </c>
+      <c r="T25" s="9"/>
     </row>
     <row r="26" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A26" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="A26" s="24"/>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
-      <c r="D26" s="23" t="s">
-        <v>51</v>
-      </c>
+      <c r="D26" s="23"/>
       <c r="E26" s="23"/>
-      <c r="F26" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F26" s="35"/>
       <c r="G26" s="35"/>
       <c r="H26" s="35"/>
-      <c r="I26" s="35">
-        <v>1</v>
-      </c>
+      <c r="I26" s="35"/>
       <c r="J26" s="35"/>
-      <c r="K26" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K26" s="23"/>
       <c r="L26" s="23"/>
-      <c r="M26" s="23" t="s">
-        <v>52</v>
-      </c>
+      <c r="M26" s="23"/>
       <c r="N26" s="23"/>
       <c r="O26" s="23"/>
       <c r="P26" s="23"/>
       <c r="Q26" s="23"/>
-      <c r="R26" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R26" s="35"/>
       <c r="S26" s="35"/>
-      <c r="T26" s="9">
-        <v>1</v>
-      </c>
+      <c r="T26" s="9"/>
     </row>
     <row r="27" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A27" s="39" t="s">
-        <v>17</v>
-      </c>
+      <c r="A27" s="39"/>
       <c r="B27" s="40"/>
       <c r="C27" s="40"/>
-      <c r="D27" s="26" t="s">
-        <v>53</v>
-      </c>
+      <c r="D27" s="26"/>
       <c r="E27" s="26"/>
-      <c r="F27" s="44" t="s">
-        <v>23</v>
-      </c>
+      <c r="F27" s="44"/>
       <c r="G27" s="44"/>
       <c r="H27" s="44"/>
-      <c r="I27" s="44">
-        <v>1</v>
-      </c>
+      <c r="I27" s="44"/>
       <c r="J27" s="44"/>
-      <c r="K27" s="26" t="s">
-        <v>17</v>
-      </c>
+      <c r="K27" s="26"/>
       <c r="L27" s="26"/>
-      <c r="M27" s="26" t="s">
-        <v>54</v>
-      </c>
+      <c r="M27" s="26"/>
       <c r="N27" s="26"/>
       <c r="O27" s="26"/>
       <c r="P27" s="26"/>
       <c r="Q27" s="26"/>
-      <c r="R27" s="44" t="s">
-        <v>23</v>
-      </c>
+      <c r="R27" s="44"/>
       <c r="S27" s="44"/>
-      <c r="T27" s="10">
-        <v>1</v>
-      </c>
+      <c r="T27" s="10"/>
     </row>
     <row r="28" spans="1:22" customHeight="1" ht="6">
       <c r="D28" s="2"/>
@@ -1977,7 +1521,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -1985,7 +1529,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -1994,12 +1538,10 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="O29" s="34"/>
-      <c r="P29" s="36" t="s">
-        <v>58</v>
-      </c>
+      <c r="P29" s="36"/>
       <c r="Q29" s="36"/>
       <c r="R29" s="36"/>
       <c r="S29" s="36"/>
@@ -2009,7 +1551,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2258,14 +1800,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -2274,7 +1816,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -2283,33 +1825,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -2443,40 +1985,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -2845,7 +2387,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -2853,7 +2395,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -2862,7 +2404,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -2875,7 +2417,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3121,102 +2663,84 @@
         <v>1</v>
       </c>
       <c r="B2" s="12"/>
-      <c r="C2" s="12" t="s">
-        <v>2</v>
-      </c>
+      <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="12"/>
-      <c r="G2" s="12" t="s">
-        <v>4</v>
-      </c>
+      <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2" s="12"/>
-      <c r="L2" s="12" t="s">
-        <v>6</v>
-      </c>
+      <c r="L2" s="12"/>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R2" s="12"/>
-      <c r="S2" s="46">
-        <v>202408300010560</v>
-      </c>
+      <c r="S2" s="46"/>
       <c r="T2" s="47"/>
     </row>
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" s="48"/>
     </row>
     <row r="5" spans="1:22" customHeight="1" ht="18">
-      <c r="A5" s="24" t="s">
-        <v>13</v>
-      </c>
+      <c r="A5" s="24"/>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="E5" s="25"/>
-      <c r="F5" s="23" t="s">
-        <v>14</v>
-      </c>
+      <c r="F5" s="23"/>
       <c r="G5" s="23"/>
       <c r="H5" s="23"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="20" t="s">
-        <v>17</v>
-      </c>
+      <c r="J5" s="20"/>
       <c r="K5" s="21"/>
       <c r="L5" s="21"/>
       <c r="M5" s="21"/>
       <c r="N5" s="22"/>
-      <c r="O5" s="20" t="s">
-        <v>18</v>
-      </c>
+      <c r="O5" s="20"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="21"/>
       <c r="R5" s="22"/>
-      <c r="S5" s="25">
-        <v>32</v>
-      </c>
+      <c r="S5" s="25"/>
       <c r="T5" s="45"/>
     </row>
     <row r="6" spans="1:22" customHeight="1" ht="18">
@@ -3327,345 +2851,217 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A12" s="42" t="s">
-        <v>17</v>
-      </c>
+      <c r="A12" s="42"/>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
-      <c r="D12" s="23" t="s">
-        <v>60</v>
-      </c>
+      <c r="D12" s="23"/>
       <c r="E12" s="23"/>
-      <c r="F12" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F12" s="35"/>
       <c r="G12" s="35"/>
       <c r="H12" s="35"/>
-      <c r="I12" s="35">
-        <v>2</v>
-      </c>
+      <c r="I12" s="35"/>
       <c r="J12" s="35"/>
-      <c r="K12" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K12" s="23"/>
       <c r="L12" s="23"/>
-      <c r="M12" s="23" t="s">
-        <v>61</v>
-      </c>
+      <c r="M12" s="23"/>
       <c r="N12" s="23"/>
       <c r="O12" s="23"/>
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R12" s="35"/>
       <c r="S12" s="35"/>
-      <c r="T12" s="9">
-        <v>2</v>
-      </c>
+      <c r="T12" s="9"/>
     </row>
     <row r="13" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A13" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="A13" s="24"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
-      <c r="D13" s="23" t="s">
-        <v>62</v>
-      </c>
+      <c r="D13" s="23"/>
       <c r="E13" s="23"/>
-      <c r="F13" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F13" s="35"/>
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
-      <c r="I13" s="35">
-        <v>2</v>
-      </c>
+      <c r="I13" s="35"/>
       <c r="J13" s="35"/>
-      <c r="K13" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K13" s="23"/>
       <c r="L13" s="23"/>
-      <c r="M13" s="23" t="s">
-        <v>63</v>
-      </c>
+      <c r="M13" s="23"/>
       <c r="N13" s="23"/>
       <c r="O13" s="23"/>
       <c r="P13" s="23"/>
       <c r="Q13" s="23"/>
-      <c r="R13" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R13" s="35"/>
       <c r="S13" s="35"/>
-      <c r="T13" s="9">
-        <v>2</v>
-      </c>
+      <c r="T13" s="9"/>
     </row>
     <row r="14" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A14" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="A14" s="24"/>
       <c r="B14" s="25"/>
       <c r="C14" s="25"/>
-      <c r="D14" s="23" t="s">
-        <v>64</v>
-      </c>
+      <c r="D14" s="23"/>
       <c r="E14" s="23"/>
-      <c r="F14" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F14" s="35"/>
       <c r="G14" s="35"/>
       <c r="H14" s="35"/>
-      <c r="I14" s="35">
-        <v>2</v>
-      </c>
+      <c r="I14" s="35"/>
       <c r="J14" s="35"/>
-      <c r="K14" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K14" s="23"/>
       <c r="L14" s="23"/>
-      <c r="M14" s="23" t="s">
-        <v>65</v>
-      </c>
+      <c r="M14" s="23"/>
       <c r="N14" s="23"/>
       <c r="O14" s="23"/>
       <c r="P14" s="23"/>
       <c r="Q14" s="23"/>
-      <c r="R14" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R14" s="35"/>
       <c r="S14" s="35"/>
-      <c r="T14" s="9">
-        <v>2</v>
-      </c>
+      <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A15" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="A15" s="24"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
-      <c r="D15" s="23" t="s">
-        <v>66</v>
-      </c>
+      <c r="D15" s="23"/>
       <c r="E15" s="23"/>
-      <c r="F15" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F15" s="35"/>
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
-      <c r="I15" s="35">
-        <v>2</v>
-      </c>
+      <c r="I15" s="35"/>
       <c r="J15" s="35"/>
-      <c r="K15" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K15" s="23"/>
       <c r="L15" s="23"/>
-      <c r="M15" s="23" t="s">
-        <v>67</v>
-      </c>
+      <c r="M15" s="23"/>
       <c r="N15" s="23"/>
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R15" s="35"/>
       <c r="S15" s="35"/>
-      <c r="T15" s="9">
-        <v>2</v>
-      </c>
+      <c r="T15" s="9"/>
     </row>
     <row r="16" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A16" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="A16" s="24"/>
       <c r="B16" s="25"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="23" t="s">
-        <v>68</v>
-      </c>
+      <c r="D16" s="23"/>
       <c r="E16" s="23"/>
-      <c r="F16" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F16" s="35"/>
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
-      <c r="I16" s="35">
-        <v>2</v>
-      </c>
+      <c r="I16" s="35"/>
       <c r="J16" s="35"/>
-      <c r="K16" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K16" s="23"/>
       <c r="L16" s="23"/>
-      <c r="M16" s="23" t="s">
-        <v>69</v>
-      </c>
+      <c r="M16" s="23"/>
       <c r="N16" s="23"/>
       <c r="O16" s="23"/>
       <c r="P16" s="23"/>
       <c r="Q16" s="23"/>
-      <c r="R16" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R16" s="35"/>
       <c r="S16" s="35"/>
-      <c r="T16" s="9">
-        <v>2</v>
-      </c>
+      <c r="T16" s="9"/>
     </row>
     <row r="17" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A17" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="A17" s="24"/>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
-      <c r="D17" s="23" t="s">
-        <v>70</v>
-      </c>
+      <c r="D17" s="23"/>
       <c r="E17" s="23"/>
-      <c r="F17" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F17" s="35"/>
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
-      <c r="I17" s="35">
-        <v>2</v>
-      </c>
+      <c r="I17" s="35"/>
       <c r="J17" s="35"/>
-      <c r="K17" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K17" s="23"/>
       <c r="L17" s="23"/>
-      <c r="M17" s="23" t="s">
-        <v>71</v>
-      </c>
+      <c r="M17" s="23"/>
       <c r="N17" s="23"/>
       <c r="O17" s="23"/>
       <c r="P17" s="23"/>
       <c r="Q17" s="23"/>
-      <c r="R17" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R17" s="35"/>
       <c r="S17" s="35"/>
-      <c r="T17" s="9">
-        <v>2</v>
-      </c>
+      <c r="T17" s="9"/>
     </row>
     <row r="18" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A18" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="A18" s="24"/>
       <c r="B18" s="25"/>
       <c r="C18" s="25"/>
-      <c r="D18" s="23" t="s">
-        <v>72</v>
-      </c>
+      <c r="D18" s="23"/>
       <c r="E18" s="23"/>
-      <c r="F18" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F18" s="35"/>
       <c r="G18" s="35"/>
       <c r="H18" s="35"/>
-      <c r="I18" s="35">
-        <v>2</v>
-      </c>
+      <c r="I18" s="35"/>
       <c r="J18" s="35"/>
-      <c r="K18" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K18" s="23"/>
       <c r="L18" s="23"/>
-      <c r="M18" s="23" t="s">
-        <v>73</v>
-      </c>
+      <c r="M18" s="23"/>
       <c r="N18" s="23"/>
       <c r="O18" s="23"/>
       <c r="P18" s="23"/>
       <c r="Q18" s="23"/>
-      <c r="R18" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R18" s="35"/>
       <c r="S18" s="35"/>
-      <c r="T18" s="9">
-        <v>2</v>
-      </c>
+      <c r="T18" s="9"/>
     </row>
     <row r="19" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A19" s="24" t="s">
-        <v>17</v>
-      </c>
+      <c r="A19" s="24"/>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
-      <c r="D19" s="23" t="s">
-        <v>74</v>
-      </c>
+      <c r="D19" s="23"/>
       <c r="E19" s="23"/>
-      <c r="F19" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="F19" s="35"/>
       <c r="G19" s="35"/>
       <c r="H19" s="35"/>
-      <c r="I19" s="35">
-        <v>2</v>
-      </c>
+      <c r="I19" s="35"/>
       <c r="J19" s="35"/>
-      <c r="K19" s="23" t="s">
-        <v>17</v>
-      </c>
+      <c r="K19" s="23"/>
       <c r="L19" s="23"/>
-      <c r="M19" s="23" t="s">
-        <v>75</v>
-      </c>
+      <c r="M19" s="23"/>
       <c r="N19" s="23"/>
       <c r="O19" s="23"/>
       <c r="P19" s="23"/>
       <c r="Q19" s="23"/>
-      <c r="R19" s="35" t="s">
-        <v>23</v>
-      </c>
+      <c r="R19" s="35"/>
       <c r="S19" s="35"/>
-      <c r="T19" s="9">
-        <v>2</v>
-      </c>
+      <c r="T19" s="9"/>
     </row>
     <row r="20" spans="1:22" customHeight="1" ht="18.6">
       <c r="A20" s="24"/>
@@ -3857,7 +3253,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -3865,7 +3261,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -3874,12 +3270,10 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="O29" s="34"/>
-      <c r="P29" s="36" t="s">
-        <v>58</v>
-      </c>
+      <c r="P29" s="36"/>
       <c r="Q29" s="36"/>
       <c r="R29" s="36"/>
       <c r="S29" s="36"/>
@@ -3889,7 +3283,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4138,14 +3532,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -4154,7 +3548,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -4163,33 +3557,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -4323,40 +3717,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -4725,7 +4119,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -4733,7 +4127,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -4742,7 +4136,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -4755,7 +4149,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -5004,14 +4398,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -5020,7 +4414,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -5029,33 +4423,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -5189,40 +4583,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -5591,7 +4985,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -5599,7 +4993,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -5608,7 +5002,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -5621,7 +5015,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -5870,14 +5264,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -5886,7 +5280,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -5895,33 +5289,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -6055,40 +5449,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -6457,7 +5851,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -6465,7 +5859,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -6474,7 +5868,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -6487,7 +5881,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -6736,14 +6130,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -6752,7 +6146,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -6761,33 +6155,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -6921,40 +6315,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -7323,7 +6717,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -7331,7 +6725,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -7340,7 +6734,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -7353,7 +6747,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -7602,14 +6996,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -7618,7 +7012,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -7627,33 +7021,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -7787,40 +7181,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -8189,7 +7583,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -8197,7 +7591,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -8206,7 +7600,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -8219,7 +7613,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -8468,14 +7862,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -8484,7 +7878,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -8493,33 +7887,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -8653,40 +8047,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -9055,7 +8449,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -9063,7 +8457,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -9072,7 +8466,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -9085,7 +8479,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -9334,14 +8728,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -9350,7 +8744,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -9359,33 +8753,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -9519,40 +8913,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -9921,7 +9315,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -9929,7 +9323,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -9938,7 +9332,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -9951,7 +9345,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/www_Test _new_lot_rull/prodout/print.xlsx
+++ b/www_Test _new_lot_rull/prodout/print.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId4"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="78">
   <si>
     <t>Drum 出 貨 檢 查 表</t>
   </si>
@@ -32,16 +32,22 @@
     <t>檢查日期</t>
   </si>
   <si>
+    <t>2024-09-13</t>
+  </si>
+  <si>
     <t>出荷日期</t>
+  </si>
+  <si>
+    <t>2024-09-16</t>
   </si>
   <si>
     <t>客戶名稱</t>
   </si>
   <si>
-    <t>出荷決定書No.</t>
+    <t>台塑勝高</t>
   </si>
   <si>
-    <t>SA20-2308081747</t>
+    <t>出荷決定書No.</t>
   </si>
   <si>
     <t>品名</t>
@@ -59,6 +65,24 @@
     <t>數量</t>
   </si>
   <si>
+    <t>HF氫氟酸</t>
+  </si>
+  <si>
+    <t>20KG BTL</t>
+  </si>
+  <si>
+    <t>F524H22B020</t>
+  </si>
+  <si>
+    <t>2025-02-22</t>
+  </si>
+  <si>
+    <t>F524I05B020</t>
+  </si>
+  <si>
+    <t>2025-03-05</t>
+  </si>
+  <si>
     <t>桶號</t>
   </si>
   <si>
@@ -66,6 +90,108 @@
   </si>
   <si>
     <t>棧板No.</t>
+  </si>
+  <si>
+    <t>FS400308</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>PM256</t>
+  </si>
+  <si>
+    <t>FS400808</t>
+  </si>
+  <si>
+    <t>FS400908</t>
+  </si>
+  <si>
+    <t>FS401108</t>
+  </si>
+  <si>
+    <t>FS401208</t>
+  </si>
+  <si>
+    <t>FS401308</t>
+  </si>
+  <si>
+    <t>FS401508</t>
+  </si>
+  <si>
+    <t>FS402008</t>
+  </si>
+  <si>
+    <t>FS402208</t>
+  </si>
+  <si>
+    <t>FS402508</t>
+  </si>
+  <si>
+    <t>FS402708</t>
+  </si>
+  <si>
+    <t>FS402808</t>
+  </si>
+  <si>
+    <t>FS403108</t>
+  </si>
+  <si>
+    <t>FS403208</t>
+  </si>
+  <si>
+    <t>FS403608</t>
+  </si>
+  <si>
+    <t>FS403708</t>
+  </si>
+  <si>
+    <t>FS404008</t>
+  </si>
+  <si>
+    <t>FS404408</t>
+  </si>
+  <si>
+    <t>FS404508</t>
+  </si>
+  <si>
+    <t>FS404708</t>
+  </si>
+  <si>
+    <t>FS404808</t>
+  </si>
+  <si>
+    <t>FS405208</t>
+  </si>
+  <si>
+    <t>FS405308</t>
+  </si>
+  <si>
+    <t>FS405508</t>
+  </si>
+  <si>
+    <t>FS405608</t>
+  </si>
+  <si>
+    <t>FS405708</t>
+  </si>
+  <si>
+    <t>FS405808</t>
+  </si>
+  <si>
+    <t>FS405908</t>
+  </si>
+  <si>
+    <t>FS406108</t>
+  </si>
+  <si>
+    <t>FS406208</t>
+  </si>
+  <si>
+    <t>FS406308</t>
+  </si>
+  <si>
+    <t>FS406408</t>
   </si>
   <si>
     <t>主管</t>
@@ -77,7 +203,61 @@
     <t>擔當</t>
   </si>
   <si>
+    <t>洪書立</t>
+  </si>
+  <si>
     <t>（QSELPC2004-001A9）</t>
+  </si>
+  <si>
+    <t>FS401509</t>
+  </si>
+  <si>
+    <t>PM291</t>
+  </si>
+  <si>
+    <t>FS401709</t>
+  </si>
+  <si>
+    <t>FS402009</t>
+  </si>
+  <si>
+    <t>FS402109</t>
+  </si>
+  <si>
+    <t>FS402209</t>
+  </si>
+  <si>
+    <t>FS402409</t>
+  </si>
+  <si>
+    <t>FS402609</t>
+  </si>
+  <si>
+    <t>FS402809</t>
+  </si>
+  <si>
+    <t>FS403009</t>
+  </si>
+  <si>
+    <t>FS404509</t>
+  </si>
+  <si>
+    <t>FS404809</t>
+  </si>
+  <si>
+    <t>FS405009</t>
+  </si>
+  <si>
+    <t>FS405409</t>
+  </si>
+  <si>
+    <t>FS405509</t>
+  </si>
+  <si>
+    <t>FS405709</t>
+  </si>
+  <si>
+    <t>FS406409</t>
   </si>
 </sst>
 </file>
@@ -929,108 +1109,134 @@
         <v>1</v>
       </c>
       <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
+      <c r="C2" s="12" t="s">
+        <v>2</v>
+      </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
+      <c r="G2" s="12" t="s">
+        <v>4</v>
+      </c>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
+      <c r="L2" s="12" t="s">
+        <v>6</v>
+      </c>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R2" s="12"/>
-      <c r="S2" s="46" t="s">
-        <v>5</v>
+      <c r="S2" s="46">
+        <v>202409120010884</v>
       </c>
       <c r="T2" s="47"/>
     </row>
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" s="48"/>
     </row>
     <row r="5" spans="1:22" customHeight="1" ht="18">
-      <c r="A5" s="24"/>
+      <c r="A5" s="24" t="s">
+        <v>13</v>
+      </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="E5" s="25"/>
-      <c r="F5" s="23"/>
+      <c r="F5" s="23" t="s">
+        <v>14</v>
+      </c>
       <c r="G5" s="23"/>
       <c r="H5" s="23"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="20"/>
+      <c r="J5" s="20" t="s">
+        <v>15</v>
+      </c>
       <c r="K5" s="21"/>
       <c r="L5" s="21"/>
       <c r="M5" s="21"/>
       <c r="N5" s="22"/>
-      <c r="O5" s="20"/>
+      <c r="O5" s="20" t="s">
+        <v>16</v>
+      </c>
       <c r="P5" s="21"/>
       <c r="Q5" s="21"/>
       <c r="R5" s="22"/>
-      <c r="S5" s="25"/>
+      <c r="S5" s="25">
+        <v>32</v>
+      </c>
       <c r="T5" s="45"/>
     </row>
     <row r="6" spans="1:22" customHeight="1" ht="18">
-      <c r="A6" s="24"/>
+      <c r="A6" s="24" t="s">
+        <v>13</v>
+      </c>
       <c r="B6" s="25"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
-      <c r="F6" s="23"/>
+      <c r="F6" s="23" t="s">
+        <v>14</v>
+      </c>
       <c r="G6" s="23"/>
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="20"/>
+      <c r="J6" s="20" t="s">
+        <v>17</v>
+      </c>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
       <c r="M6" s="21"/>
       <c r="N6" s="22"/>
-      <c r="O6" s="20"/>
+      <c r="O6" s="20" t="s">
+        <v>18</v>
+      </c>
       <c r="P6" s="21"/>
       <c r="Q6" s="21"/>
       <c r="R6" s="22"/>
-      <c r="S6" s="25"/>
+      <c r="S6" s="25">
+        <v>16</v>
+      </c>
       <c r="T6" s="45"/>
     </row>
     <row r="7" spans="1:22" customHeight="1" ht="18">
@@ -1119,393 +1325,649 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A12" s="42"/>
+      <c r="A12" s="42" t="s">
+        <v>15</v>
+      </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
+      <c r="D12" s="23" t="s">
+        <v>22</v>
+      </c>
       <c r="E12" s="23"/>
-      <c r="F12" s="35"/>
+      <c r="F12" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G12" s="35"/>
       <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
+      <c r="I12" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J12" s="35"/>
-      <c r="K12" s="23"/>
+      <c r="K12" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
+      <c r="M12" s="23" t="s">
+        <v>25</v>
+      </c>
       <c r="N12" s="23"/>
       <c r="O12" s="23"/>
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="35"/>
+      <c r="R12" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S12" s="35"/>
-      <c r="T12" s="9"/>
+      <c r="T12" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="13" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A13" s="24"/>
+      <c r="A13" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="23" t="s">
+        <v>26</v>
+      </c>
       <c r="E13" s="23"/>
-      <c r="F13" s="35"/>
+      <c r="F13" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
+      <c r="I13" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J13" s="35"/>
-      <c r="K13" s="23"/>
+      <c r="K13" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
+      <c r="M13" s="23" t="s">
+        <v>27</v>
+      </c>
       <c r="N13" s="23"/>
       <c r="O13" s="23"/>
       <c r="P13" s="23"/>
       <c r="Q13" s="23"/>
-      <c r="R13" s="35"/>
+      <c r="R13" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S13" s="35"/>
-      <c r="T13" s="9"/>
+      <c r="T13" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="14" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A14" s="24"/>
+      <c r="A14" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B14" s="25"/>
       <c r="C14" s="25"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="23" t="s">
+        <v>28</v>
+      </c>
       <c r="E14" s="23"/>
-      <c r="F14" s="35"/>
+      <c r="F14" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G14" s="35"/>
       <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
+      <c r="I14" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J14" s="35"/>
-      <c r="K14" s="23"/>
+      <c r="K14" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
+      <c r="M14" s="23" t="s">
+        <v>29</v>
+      </c>
       <c r="N14" s="23"/>
       <c r="O14" s="23"/>
       <c r="P14" s="23"/>
       <c r="Q14" s="23"/>
-      <c r="R14" s="35"/>
+      <c r="R14" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S14" s="35"/>
-      <c r="T14" s="9"/>
+      <c r="T14" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="15" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A15" s="24"/>
+      <c r="A15" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="23" t="s">
+        <v>30</v>
+      </c>
       <c r="E15" s="23"/>
-      <c r="F15" s="35"/>
+      <c r="F15" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
+      <c r="I15" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J15" s="35"/>
-      <c r="K15" s="23"/>
+      <c r="K15" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
+      <c r="M15" s="23" t="s">
+        <v>31</v>
+      </c>
       <c r="N15" s="23"/>
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="35"/>
+      <c r="R15" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S15" s="35"/>
-      <c r="T15" s="9"/>
+      <c r="T15" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="16" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A16" s="24"/>
+      <c r="A16" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B16" s="25"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="23" t="s">
+        <v>32</v>
+      </c>
       <c r="E16" s="23"/>
-      <c r="F16" s="35"/>
+      <c r="F16" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
+      <c r="I16" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J16" s="35"/>
-      <c r="K16" s="23"/>
+      <c r="K16" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
+      <c r="M16" s="23" t="s">
+        <v>33</v>
+      </c>
       <c r="N16" s="23"/>
       <c r="O16" s="23"/>
       <c r="P16" s="23"/>
       <c r="Q16" s="23"/>
-      <c r="R16" s="35"/>
+      <c r="R16" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S16" s="35"/>
-      <c r="T16" s="9"/>
+      <c r="T16" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="17" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A17" s="24"/>
+      <c r="A17" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
-      <c r="D17" s="23"/>
+      <c r="D17" s="23" t="s">
+        <v>34</v>
+      </c>
       <c r="E17" s="23"/>
-      <c r="F17" s="35"/>
+      <c r="F17" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
+      <c r="I17" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J17" s="35"/>
-      <c r="K17" s="23"/>
+      <c r="K17" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
+      <c r="M17" s="23" t="s">
+        <v>35</v>
+      </c>
       <c r="N17" s="23"/>
       <c r="O17" s="23"/>
       <c r="P17" s="23"/>
       <c r="Q17" s="23"/>
-      <c r="R17" s="35"/>
+      <c r="R17" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S17" s="35"/>
-      <c r="T17" s="9"/>
+      <c r="T17" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="18" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A18" s="24"/>
+      <c r="A18" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B18" s="25"/>
       <c r="C18" s="25"/>
-      <c r="D18" s="23"/>
+      <c r="D18" s="23" t="s">
+        <v>36</v>
+      </c>
       <c r="E18" s="23"/>
-      <c r="F18" s="35"/>
+      <c r="F18" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G18" s="35"/>
       <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
+      <c r="I18" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J18" s="35"/>
-      <c r="K18" s="23"/>
+      <c r="K18" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
+      <c r="M18" s="23" t="s">
+        <v>37</v>
+      </c>
       <c r="N18" s="23"/>
       <c r="O18" s="23"/>
       <c r="P18" s="23"/>
       <c r="Q18" s="23"/>
-      <c r="R18" s="35"/>
+      <c r="R18" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S18" s="35"/>
-      <c r="T18" s="9"/>
+      <c r="T18" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="19" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A19" s="24"/>
+      <c r="A19" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
-      <c r="D19" s="23"/>
+      <c r="D19" s="23" t="s">
+        <v>38</v>
+      </c>
       <c r="E19" s="23"/>
-      <c r="F19" s="35"/>
+      <c r="F19" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G19" s="35"/>
       <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
+      <c r="I19" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J19" s="35"/>
-      <c r="K19" s="23"/>
+      <c r="K19" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
+      <c r="M19" s="23" t="s">
+        <v>39</v>
+      </c>
       <c r="N19" s="23"/>
       <c r="O19" s="23"/>
       <c r="P19" s="23"/>
       <c r="Q19" s="23"/>
-      <c r="R19" s="35"/>
+      <c r="R19" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S19" s="35"/>
-      <c r="T19" s="9"/>
+      <c r="T19" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="20" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A20" s="24"/>
+      <c r="A20" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B20" s="25"/>
       <c r="C20" s="25"/>
-      <c r="D20" s="23"/>
+      <c r="D20" s="23" t="s">
+        <v>40</v>
+      </c>
       <c r="E20" s="23"/>
-      <c r="F20" s="35"/>
+      <c r="F20" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G20" s="35"/>
       <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
+      <c r="I20" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J20" s="35"/>
-      <c r="K20" s="23"/>
+      <c r="K20" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
+      <c r="M20" s="23" t="s">
+        <v>41</v>
+      </c>
       <c r="N20" s="23"/>
       <c r="O20" s="23"/>
       <c r="P20" s="23"/>
       <c r="Q20" s="23"/>
-      <c r="R20" s="35"/>
+      <c r="R20" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S20" s="35"/>
-      <c r="T20" s="9"/>
+      <c r="T20" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="21" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A21" s="24"/>
+      <c r="A21" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
-      <c r="D21" s="23"/>
+      <c r="D21" s="23" t="s">
+        <v>42</v>
+      </c>
       <c r="E21" s="23"/>
-      <c r="F21" s="35"/>
+      <c r="F21" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G21" s="35"/>
       <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
+      <c r="I21" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J21" s="35"/>
-      <c r="K21" s="23"/>
+      <c r="K21" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L21" s="23"/>
-      <c r="M21" s="23"/>
+      <c r="M21" s="23" t="s">
+        <v>43</v>
+      </c>
       <c r="N21" s="23"/>
       <c r="O21" s="23"/>
       <c r="P21" s="23"/>
       <c r="Q21" s="23"/>
-      <c r="R21" s="35"/>
+      <c r="R21" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S21" s="35"/>
-      <c r="T21" s="9"/>
+      <c r="T21" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="22" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A22" s="24"/>
+      <c r="A22" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B22" s="25"/>
       <c r="C22" s="25"/>
-      <c r="D22" s="23"/>
+      <c r="D22" s="23" t="s">
+        <v>44</v>
+      </c>
       <c r="E22" s="23"/>
-      <c r="F22" s="35"/>
+      <c r="F22" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G22" s="35"/>
       <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
+      <c r="I22" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J22" s="35"/>
-      <c r="K22" s="23"/>
+      <c r="K22" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
+      <c r="M22" s="23" t="s">
+        <v>45</v>
+      </c>
       <c r="N22" s="23"/>
       <c r="O22" s="23"/>
       <c r="P22" s="23"/>
       <c r="Q22" s="23"/>
-      <c r="R22" s="35"/>
+      <c r="R22" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S22" s="35"/>
-      <c r="T22" s="9"/>
+      <c r="T22" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="23" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A23" s="24"/>
+      <c r="A23" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
-      <c r="D23" s="23"/>
+      <c r="D23" s="23" t="s">
+        <v>46</v>
+      </c>
       <c r="E23" s="23"/>
-      <c r="F23" s="35"/>
+      <c r="F23" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G23" s="35"/>
       <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
+      <c r="I23" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J23" s="35"/>
-      <c r="K23" s="23"/>
+      <c r="K23" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
+      <c r="M23" s="23" t="s">
+        <v>47</v>
+      </c>
       <c r="N23" s="23"/>
       <c r="O23" s="23"/>
       <c r="P23" s="23"/>
       <c r="Q23" s="23"/>
-      <c r="R23" s="35"/>
+      <c r="R23" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S23" s="35"/>
-      <c r="T23" s="9"/>
+      <c r="T23" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="24" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A24" s="24"/>
+      <c r="A24" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
-      <c r="D24" s="23"/>
+      <c r="D24" s="23" t="s">
+        <v>48</v>
+      </c>
       <c r="E24" s="23"/>
-      <c r="F24" s="35"/>
+      <c r="F24" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G24" s="35"/>
       <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
+      <c r="I24" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J24" s="35"/>
-      <c r="K24" s="23"/>
+      <c r="K24" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
+      <c r="M24" s="23" t="s">
+        <v>49</v>
+      </c>
       <c r="N24" s="23"/>
       <c r="O24" s="23"/>
       <c r="P24" s="23"/>
       <c r="Q24" s="23"/>
-      <c r="R24" s="35"/>
+      <c r="R24" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S24" s="35"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="25" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A25" s="24"/>
+      <c r="A25" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
-      <c r="D25" s="23"/>
+      <c r="D25" s="23" t="s">
+        <v>50</v>
+      </c>
       <c r="E25" s="23"/>
-      <c r="F25" s="35"/>
+      <c r="F25" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G25" s="35"/>
       <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
+      <c r="I25" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J25" s="35"/>
-      <c r="K25" s="23"/>
+      <c r="K25" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
+      <c r="M25" s="23" t="s">
+        <v>51</v>
+      </c>
       <c r="N25" s="23"/>
       <c r="O25" s="23"/>
       <c r="P25" s="23"/>
       <c r="Q25" s="23"/>
-      <c r="R25" s="35"/>
+      <c r="R25" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S25" s="35"/>
-      <c r="T25" s="9"/>
+      <c r="T25" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="26" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A26" s="24"/>
+      <c r="A26" s="24" t="s">
+        <v>15</v>
+      </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
-      <c r="D26" s="23"/>
+      <c r="D26" s="23" t="s">
+        <v>52</v>
+      </c>
       <c r="E26" s="23"/>
-      <c r="F26" s="35"/>
+      <c r="F26" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G26" s="35"/>
       <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
+      <c r="I26" s="35" t="s">
+        <v>24</v>
+      </c>
       <c r="J26" s="35"/>
-      <c r="K26" s="23"/>
+      <c r="K26" s="23" t="s">
+        <v>15</v>
+      </c>
       <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
+      <c r="M26" s="23" t="s">
+        <v>53</v>
+      </c>
       <c r="N26" s="23"/>
       <c r="O26" s="23"/>
       <c r="P26" s="23"/>
       <c r="Q26" s="23"/>
-      <c r="R26" s="35"/>
+      <c r="R26" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S26" s="35"/>
-      <c r="T26" s="9"/>
+      <c r="T26" s="9" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="27" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A27" s="39"/>
+      <c r="A27" s="39" t="s">
+        <v>15</v>
+      </c>
       <c r="B27" s="40"/>
       <c r="C27" s="40"/>
-      <c r="D27" s="26"/>
+      <c r="D27" s="26" t="s">
+        <v>54</v>
+      </c>
       <c r="E27" s="26"/>
-      <c r="F27" s="44"/>
+      <c r="F27" s="44" t="s">
+        <v>23</v>
+      </c>
       <c r="G27" s="44"/>
       <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
+      <c r="I27" s="44" t="s">
+        <v>24</v>
+      </c>
       <c r="J27" s="44"/>
-      <c r="K27" s="26"/>
+      <c r="K27" s="26" t="s">
+        <v>15</v>
+      </c>
       <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
+      <c r="M27" s="26" t="s">
+        <v>55</v>
+      </c>
       <c r="N27" s="26"/>
       <c r="O27" s="26"/>
       <c r="P27" s="26"/>
       <c r="Q27" s="26"/>
-      <c r="R27" s="44"/>
+      <c r="R27" s="44" t="s">
+        <v>23</v>
+      </c>
       <c r="S27" s="44"/>
-      <c r="T27" s="10"/>
+      <c r="T27" s="10" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="28" spans="1:22" customHeight="1" ht="6">
       <c r="D28" s="2"/>
@@ -1521,7 +1983,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -1529,7 +1991,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -1538,10 +2000,12 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="O29" s="34"/>
-      <c r="P29" s="36"/>
+      <c r="P29" s="36" t="s">
+        <v>59</v>
+      </c>
       <c r="Q29" s="36"/>
       <c r="R29" s="36"/>
       <c r="S29" s="36"/>
@@ -1551,7 +2015,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1800,14 +2264,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -1816,7 +2280,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -1825,33 +2289,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -1985,40 +2449,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -2387,7 +2851,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -2395,7 +2859,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -2404,7 +2868,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -2417,7 +2881,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2663,106 +3127,134 @@
         <v>1</v>
       </c>
       <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
+      <c r="C2" s="12" t="s">
+        <v>2</v>
+      </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
+      <c r="G2" s="12" t="s">
+        <v>4</v>
+      </c>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
+      <c r="L2" s="12" t="s">
+        <v>6</v>
+      </c>
       <c r="M2" s="12"/>
       <c r="N2" s="12"/>
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R2" s="12"/>
-      <c r="S2" s="46"/>
+      <c r="S2" s="46">
+        <v>202409120010884</v>
+      </c>
       <c r="T2" s="47"/>
     </row>
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" s="48"/>
     </row>
     <row r="5" spans="1:22" customHeight="1" ht="18">
-      <c r="A5" s="24"/>
+      <c r="A5" s="24" t="s">
+        <v>13</v>
+      </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="E5" s="25"/>
-      <c r="F5" s="23"/>
+      <c r="F5" s="23" t="s">
+        <v>14</v>
+      </c>
       <c r="G5" s="23"/>
       <c r="H5" s="23"/>
       <c r="I5" s="23"/>
-      <c r="J5" s="20"/>
+      <c r="J5" s="20" t="s">
+        <v>17</v>
+      </c>
       <c r="K5" s="21"/>
       <c r="L5" s="21"/>
       <c r="M5" s="21"/>
       <c r="N5" s="22"/>
-      <c r="O5" s="20"/>
+      <c r="O5" s="20" t="s">
+        <v>18</v>
+      </c>
       <c r="P5" s="21"/>
       <c r="Q5" s="21"/>
       <c r="R5" s="22"/>
-      <c r="S5" s="25"/>
+      <c r="S5" s="25">
+        <v>16</v>
+      </c>
       <c r="T5" s="45"/>
     </row>
     <row r="6" spans="1:22" customHeight="1" ht="18">
-      <c r="A6" s="24"/>
+      <c r="A6" s="24" t="s">
+        <v>13</v>
+      </c>
       <c r="B6" s="25"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
-      <c r="F6" s="23"/>
+      <c r="F6" s="23" t="s">
+        <v>14</v>
+      </c>
       <c r="G6" s="23"/>
       <c r="H6" s="23"/>
       <c r="I6" s="23"/>
-      <c r="J6" s="20"/>
+      <c r="J6" s="20" t="s">
+        <v>15</v>
+      </c>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
       <c r="M6" s="21"/>
       <c r="N6" s="22"/>
-      <c r="O6" s="20"/>
+      <c r="O6" s="20" t="s">
+        <v>16</v>
+      </c>
       <c r="P6" s="21"/>
       <c r="Q6" s="21"/>
       <c r="R6" s="22"/>
-      <c r="S6" s="25"/>
+      <c r="S6" s="25">
+        <v>32</v>
+      </c>
       <c r="T6" s="45"/>
     </row>
     <row r="7" spans="1:22" customHeight="1" ht="18">
@@ -2851,217 +3343,345 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A12" s="42"/>
+      <c r="A12" s="42" t="s">
+        <v>17</v>
+      </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
+      <c r="D12" s="23" t="s">
+        <v>61</v>
+      </c>
       <c r="E12" s="23"/>
-      <c r="F12" s="35"/>
+      <c r="F12" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G12" s="35"/>
       <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
+      <c r="I12" s="35" t="s">
+        <v>62</v>
+      </c>
       <c r="J12" s="35"/>
-      <c r="K12" s="23"/>
+      <c r="K12" s="23" t="s">
+        <v>17</v>
+      </c>
       <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
+      <c r="M12" s="23" t="s">
+        <v>63</v>
+      </c>
       <c r="N12" s="23"/>
       <c r="O12" s="23"/>
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
-      <c r="R12" s="35"/>
+      <c r="R12" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S12" s="35"/>
-      <c r="T12" s="9"/>
+      <c r="T12" s="9" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="13" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A13" s="24"/>
+      <c r="A13" s="24" t="s">
+        <v>17</v>
+      </c>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
-      <c r="D13" s="23"/>
+      <c r="D13" s="23" t="s">
+        <v>64</v>
+      </c>
       <c r="E13" s="23"/>
-      <c r="F13" s="35"/>
+      <c r="F13" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G13" s="35"/>
       <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
+      <c r="I13" s="35" t="s">
+        <v>62</v>
+      </c>
       <c r="J13" s="35"/>
-      <c r="K13" s="23"/>
+      <c r="K13" s="23" t="s">
+        <v>17</v>
+      </c>
       <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
+      <c r="M13" s="23" t="s">
+        <v>65</v>
+      </c>
       <c r="N13" s="23"/>
       <c r="O13" s="23"/>
       <c r="P13" s="23"/>
       <c r="Q13" s="23"/>
-      <c r="R13" s="35"/>
+      <c r="R13" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S13" s="35"/>
-      <c r="T13" s="9"/>
+      <c r="T13" s="9" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="14" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A14" s="24"/>
+      <c r="A14" s="24" t="s">
+        <v>17</v>
+      </c>
       <c r="B14" s="25"/>
       <c r="C14" s="25"/>
-      <c r="D14" s="23"/>
+      <c r="D14" s="23" t="s">
+        <v>66</v>
+      </c>
       <c r="E14" s="23"/>
-      <c r="F14" s="35"/>
+      <c r="F14" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G14" s="35"/>
       <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
+      <c r="I14" s="35" t="s">
+        <v>62</v>
+      </c>
       <c r="J14" s="35"/>
-      <c r="K14" s="23"/>
+      <c r="K14" s="23" t="s">
+        <v>17</v>
+      </c>
       <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
+      <c r="M14" s="23" t="s">
+        <v>67</v>
+      </c>
       <c r="N14" s="23"/>
       <c r="O14" s="23"/>
       <c r="P14" s="23"/>
       <c r="Q14" s="23"/>
-      <c r="R14" s="35"/>
+      <c r="R14" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S14" s="35"/>
-      <c r="T14" s="9"/>
+      <c r="T14" s="9" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="15" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A15" s="24"/>
+      <c r="A15" s="24" t="s">
+        <v>17</v>
+      </c>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="23" t="s">
+        <v>68</v>
+      </c>
       <c r="E15" s="23"/>
-      <c r="F15" s="35"/>
+      <c r="F15" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G15" s="35"/>
       <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
+      <c r="I15" s="35" t="s">
+        <v>62</v>
+      </c>
       <c r="J15" s="35"/>
-      <c r="K15" s="23"/>
+      <c r="K15" s="23" t="s">
+        <v>17</v>
+      </c>
       <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
+      <c r="M15" s="23" t="s">
+        <v>69</v>
+      </c>
       <c r="N15" s="23"/>
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="35"/>
+      <c r="R15" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S15" s="35"/>
-      <c r="T15" s="9"/>
+      <c r="T15" s="9" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="16" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A16" s="24"/>
+      <c r="A16" s="24" t="s">
+        <v>17</v>
+      </c>
       <c r="B16" s="25"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="23"/>
+      <c r="D16" s="23" t="s">
+        <v>70</v>
+      </c>
       <c r="E16" s="23"/>
-      <c r="F16" s="35"/>
+      <c r="F16" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
-      <c r="I16" s="35"/>
+      <c r="I16" s="35" t="s">
+        <v>62</v>
+      </c>
       <c r="J16" s="35"/>
-      <c r="K16" s="23"/>
+      <c r="K16" s="23" t="s">
+        <v>17</v>
+      </c>
       <c r="L16" s="23"/>
-      <c r="M16" s="23"/>
+      <c r="M16" s="23" t="s">
+        <v>71</v>
+      </c>
       <c r="N16" s="23"/>
       <c r="O16" s="23"/>
       <c r="P16" s="23"/>
       <c r="Q16" s="23"/>
-      <c r="R16" s="35"/>
+      <c r="R16" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S16" s="35"/>
-      <c r="T16" s="9"/>
+      <c r="T16" s="9" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="17" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A17" s="24"/>
+      <c r="A17" s="24" t="s">
+        <v>17</v>
+      </c>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
-      <c r="D17" s="23"/>
+      <c r="D17" s="23" t="s">
+        <v>72</v>
+      </c>
       <c r="E17" s="23"/>
-      <c r="F17" s="35"/>
+      <c r="F17" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G17" s="35"/>
       <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
+      <c r="I17" s="35" t="s">
+        <v>62</v>
+      </c>
       <c r="J17" s="35"/>
-      <c r="K17" s="23"/>
+      <c r="K17" s="23" t="s">
+        <v>17</v>
+      </c>
       <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
+      <c r="M17" s="23" t="s">
+        <v>73</v>
+      </c>
       <c r="N17" s="23"/>
       <c r="O17" s="23"/>
       <c r="P17" s="23"/>
       <c r="Q17" s="23"/>
-      <c r="R17" s="35"/>
+      <c r="R17" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S17" s="35"/>
-      <c r="T17" s="9"/>
+      <c r="T17" s="9" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="18" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A18" s="24"/>
+      <c r="A18" s="24" t="s">
+        <v>17</v>
+      </c>
       <c r="B18" s="25"/>
       <c r="C18" s="25"/>
-      <c r="D18" s="23"/>
+      <c r="D18" s="23" t="s">
+        <v>74</v>
+      </c>
       <c r="E18" s="23"/>
-      <c r="F18" s="35"/>
+      <c r="F18" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G18" s="35"/>
       <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
+      <c r="I18" s="35" t="s">
+        <v>62</v>
+      </c>
       <c r="J18" s="35"/>
-      <c r="K18" s="23"/>
+      <c r="K18" s="23" t="s">
+        <v>17</v>
+      </c>
       <c r="L18" s="23"/>
-      <c r="M18" s="23"/>
+      <c r="M18" s="23" t="s">
+        <v>75</v>
+      </c>
       <c r="N18" s="23"/>
       <c r="O18" s="23"/>
       <c r="P18" s="23"/>
       <c r="Q18" s="23"/>
-      <c r="R18" s="35"/>
+      <c r="R18" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S18" s="35"/>
-      <c r="T18" s="9"/>
+      <c r="T18" s="9" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="19" spans="1:22" customHeight="1" ht="18.6">
-      <c r="A19" s="24"/>
+      <c r="A19" s="24" t="s">
+        <v>17</v>
+      </c>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
-      <c r="D19" s="23"/>
+      <c r="D19" s="23" t="s">
+        <v>76</v>
+      </c>
       <c r="E19" s="23"/>
-      <c r="F19" s="35"/>
+      <c r="F19" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="G19" s="35"/>
       <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
+      <c r="I19" s="35" t="s">
+        <v>62</v>
+      </c>
       <c r="J19" s="35"/>
-      <c r="K19" s="23"/>
+      <c r="K19" s="23" t="s">
+        <v>17</v>
+      </c>
       <c r="L19" s="23"/>
-      <c r="M19" s="23"/>
+      <c r="M19" s="23" t="s">
+        <v>77</v>
+      </c>
       <c r="N19" s="23"/>
       <c r="O19" s="23"/>
       <c r="P19" s="23"/>
       <c r="Q19" s="23"/>
-      <c r="R19" s="35"/>
+      <c r="R19" s="35" t="s">
+        <v>23</v>
+      </c>
       <c r="S19" s="35"/>
-      <c r="T19" s="9"/>
+      <c r="T19" s="9" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="20" spans="1:22" customHeight="1" ht="18.6">
       <c r="A20" s="24"/>
@@ -3253,7 +3873,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -3261,7 +3881,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -3270,10 +3890,12 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="O29" s="34"/>
-      <c r="P29" s="36"/>
+      <c r="P29" s="36" t="s">
+        <v>59</v>
+      </c>
       <c r="Q29" s="36"/>
       <c r="R29" s="36"/>
       <c r="S29" s="36"/>
@@ -3283,7 +3905,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3532,14 +4154,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -3548,7 +4170,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -3557,33 +4179,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -3717,40 +4339,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -4119,7 +4741,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -4127,7 +4749,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -4136,7 +4758,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -4149,7 +4771,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4398,14 +5020,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -4414,7 +5036,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -4423,33 +5045,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -4583,40 +5205,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -4985,7 +5607,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -4993,7 +5615,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -5002,7 +5624,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -5015,7 +5637,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -5264,14 +5886,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -5280,7 +5902,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -5289,33 +5911,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -5449,40 +6071,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -5851,7 +6473,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -5859,7 +6481,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -5868,7 +6490,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -5881,7 +6503,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -6130,14 +6752,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -6146,7 +6768,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -6155,33 +6777,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -6315,40 +6937,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -6717,7 +7339,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -6725,7 +7347,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -6734,7 +7356,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -6747,7 +7369,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -6996,14 +7618,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -7012,7 +7634,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -7021,33 +7643,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -7181,40 +7803,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -7583,7 +8205,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -7591,7 +8213,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -7600,7 +8222,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -7613,7 +8235,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -7862,14 +8484,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -7878,7 +8500,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -7887,33 +8509,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -8047,40 +8669,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -8449,7 +9071,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -8457,7 +9079,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -8466,7 +9088,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -8479,7 +9101,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -8728,14 +9350,14 @@
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="12" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -8744,7 +9366,7 @@
       <c r="O2" s="12"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R2" s="12"/>
       <c r="S2" s="46"/>
@@ -8753,33 +9375,33 @@
     <row r="3" spans="1:22" customHeight="1" ht="4.5"/>
     <row r="4" spans="1:22" customHeight="1" ht="18">
       <c r="A4" s="27" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="17" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K4" s="18"/>
       <c r="L4" s="18"/>
       <c r="M4" s="18"/>
       <c r="N4" s="19"/>
       <c r="O4" s="14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
       <c r="R4" s="16"/>
       <c r="S4" s="28" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" s="48"/>
     </row>
@@ -8913,40 +9535,40 @@
     </row>
     <row r="11" spans="1:22" customHeight="1" ht="18.6">
       <c r="A11" s="27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G11" s="29"/>
       <c r="H11" s="29"/>
       <c r="I11" s="28" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J11" s="28"/>
       <c r="K11" s="28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L11" s="28"/>
       <c r="M11" s="29" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
       <c r="R11" s="29" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S11" s="29"/>
       <c r="T11" s="6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:22" customHeight="1" ht="18.6">
@@ -9315,7 +9937,7 @@
     </row>
     <row r="29" spans="1:22" customHeight="1" ht="48">
       <c r="A29" s="7" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -9323,7 +9945,7 @@
       <c r="E29" s="12"/>
       <c r="F29" s="13"/>
       <c r="G29" s="8" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
@@ -9332,7 +9954,7 @@
       <c r="L29" s="36"/>
       <c r="M29" s="37"/>
       <c r="N29" s="33" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="O29" s="34"/>
       <c r="P29" s="36"/>
@@ -9345,7 +9967,7 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="11" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
